--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.93532596212454</v>
+        <v>5.026990468845238</v>
       </c>
       <c r="D2" t="n">
-        <v>30.77991742084718</v>
+        <v>5.001736580887667</v>
       </c>
       <c r="E2" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F2" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.82547116742254</v>
+        <v>3.709139064706163</v>
       </c>
       <c r="D3" t="n">
-        <v>23.06443462616738</v>
+        <v>3.7479706267522</v>
       </c>
       <c r="E3" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F3" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.57320610062443</v>
+        <v>3.018145991351469</v>
       </c>
       <c r="D4" t="n">
-        <v>18.35543605189504</v>
+        <v>2.982758358432944</v>
       </c>
       <c r="E4" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F4" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.93318576728286</v>
+        <v>5.514142687183464</v>
       </c>
       <c r="D5" t="n">
-        <v>33.4522231744014</v>
+        <v>5.435986265840229</v>
       </c>
       <c r="E5" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F5" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.99351248788175</v>
+        <v>4.711445779280785</v>
       </c>
       <c r="D6" t="n">
-        <v>28.49580300210634</v>
+        <v>4.630567987842279</v>
       </c>
       <c r="E6" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F6" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.22773778457753</v>
+        <v>5.237007389993848</v>
       </c>
       <c r="D7" t="n">
-        <v>31.74798887402831</v>
+        <v>5.159048192029601</v>
       </c>
       <c r="E7" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F7" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.4383132750967</v>
+        <v>5.596225907203213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.99451109885371</v>
+        <v>5.524108053563728</v>
       </c>
       <c r="E8" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F8" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.92734271957478</v>
+        <v>2.263193191930902</v>
       </c>
       <c r="D9" t="n">
-        <v>13.447630520729</v>
+        <v>2.185239959618464</v>
       </c>
       <c r="E9" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F9" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.93743304410413</v>
+        <v>5.514832869666922</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73977714921293</v>
+        <v>5.482713786747102</v>
       </c>
       <c r="E10" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F10" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81570055823563</v>
+        <v>3.87005134071329</v>
       </c>
       <c r="D11" t="n">
-        <v>23.59668610941796</v>
+        <v>3.834461492780418</v>
       </c>
       <c r="E11" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F11" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.261125793094652</v>
+        <v>0.854932941377881</v>
       </c>
       <c r="D12" t="n">
-        <v>5.382168455854587</v>
+        <v>0.8746023740763704</v>
       </c>
       <c r="E12" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F12" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.23821018588692</v>
+        <v>3.776209155206624</v>
       </c>
       <c r="D13" t="n">
-        <v>23.5450501736785</v>
+        <v>3.826070653222756</v>
       </c>
       <c r="E13" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F13" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.72447696370317</v>
+        <v>3.855227506601765</v>
       </c>
       <c r="D14" t="n">
-        <v>23.83501188194743</v>
+        <v>3.873189430816458</v>
       </c>
       <c r="E14" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F14" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.21497854258169</v>
+        <v>5.072434013169524</v>
       </c>
       <c r="D15" t="n">
-        <v>31.56117009833772</v>
+        <v>5.128690140979879</v>
       </c>
       <c r="E15" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F15" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.07499026486445</v>
+        <v>4.724685918040473</v>
       </c>
       <c r="D16" t="n">
-        <v>29.5525854713318</v>
+        <v>4.802295139091417</v>
       </c>
       <c r="E16" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F16" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>30.28844212996519</v>
+        <v>4.921871846119344</v>
       </c>
       <c r="D17" t="n">
-        <v>30.70773711275467</v>
+        <v>4.990007280822634</v>
       </c>
       <c r="E17" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F17" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>5.538945943473141</v>
+        <v>0.9000787158143855</v>
       </c>
       <c r="D18" t="n">
-        <v>8.120774930063739</v>
+        <v>1.319625926135358</v>
       </c>
       <c r="E18" t="n">
-        <v>9.00311792489631</v>
+        <v>1.46300666279565</v>
       </c>
       <c r="F18" t="n">
-        <v>8.652275858553557</v>
+        <v>1.405994827014953</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
